--- a/지비스_제품가격표.xlsx
+++ b/지비스_제품가격표.xlsx
@@ -323,6 +323,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -348,6 +351,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -373,6 +379,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -398,6 +407,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -423,6 +435,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -448,6 +463,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -473,6 +491,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -498,6 +519,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -523,6 +547,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -548,6 +575,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -573,6 +603,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -598,6 +631,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -623,6 +659,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -648,6 +687,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -673,6 +715,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -698,6 +743,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -723,6 +771,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -748,6 +799,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -773,6 +827,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -798,6 +855,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -823,6 +883,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1119,7 +1182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1754,7 +1817,7 @@
         </is>
       </c>
       <c r="F23" s="16" t="n">
-        <v>37500</v>
+        <v>24500</v>
       </c>
       <c r="G23" s="17" t="inlineStr">
         <is>
@@ -1783,11 +1846,39 @@
         </is>
       </c>
       <c r="F24" s="9" t="n">
-        <v>46200</v>
+        <v>30100</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
           <t>상세보기 →</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>22</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>컨버터/액세서리</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>컨버터 150W IoT</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>150W</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>44100</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/지비스_제품가격표.xlsx
+++ b/지비스_제품가격표.xlsx
@@ -1182,7 +1182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="F20" s="23" t="n">
-        <v>24000</v>
+        <v>50000</v>
       </c>
       <c r="G20" s="24" t="inlineStr">
         <is>
@@ -1877,6 +1877,34 @@
         <v>44100</v>
       </c>
       <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>컨버터/액세서리</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>컨트롤러 2-Wire</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2-Wire 디밍</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>35000</v>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/지비스_제품가격표.xlsx
+++ b/지비스_제품가격표.xlsx
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="F19" s="23" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="G19" s="24" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="F20" s="23" t="n">
-        <v>50000</v>
+        <v>77500</v>
       </c>
       <c r="G20" s="24" t="inlineStr">
         <is>

--- a/지비스_제품가격표.xlsx
+++ b/지비스_제품가격표.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0&quot;원&quot;"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,6 +91,21 @@
       <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -156,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -222,6 +237,19 @@
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1182,7 +1210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1286,16 +1314,16 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>IoT 컷오프 스마트 원형 다운라이트 2인치/3인치</t>
+          <t>IoT 컷오프 스마트 원형 다운라이트 2인치</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>2인치/3인치 | 컷오프 설계</t>
+          <t>2인치 | 컷오프 설계</t>
         </is>
       </c>
       <c r="F5" s="16" t="n">
-        <v>22000</v>
+        <v>9000</v>
       </c>
       <c r="G5" s="17" t="inlineStr">
         <is>
@@ -1304,406 +1332,406 @@
       </c>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="inlineStr"/>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="B6" s="25" t="n"/>
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>원형 다운라이트</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>IoT 컷오프 스마트 원형 다운라이트 3인치</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>3인치 | 컷오프 설계</t>
+        </is>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>9700</v>
+      </c>
+      <c r="G6" s="29" t="inlineStr">
+        <is>
+          <t>상세보기 →</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>원형 다운라이트</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>IoT 사이렌 스마트 원형 다운라이트 2인치</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>2인치 | 집중형·확산형 선택</t>
         </is>
       </c>
-      <c r="F6" s="9" t="n">
-        <v>22000</v>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>상세보기 →</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="12" t="inlineStr"/>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="F7" s="9" t="n">
+        <v>17900</v>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>상세보기 →</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr"/>
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>원형 다운라이트</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>IoT 스마트 초소형 원형 매립등 1.5인치</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>1.5인치 | 31mm 타공</t>
         </is>
       </c>
-      <c r="F7" s="16" t="n">
-        <v>35000</v>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>상세보기 →</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="F8" s="16" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>상세보기 →</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>원형 다운라이트</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>IoT_다운라이트 2인치 (3W)</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>2인치 | 3W</t>
         </is>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F9" s="9" t="n">
         <v>16300</v>
       </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>상세보기 →</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="12" t="inlineStr"/>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>상세보기 →</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="12" t="inlineStr"/>
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>원형 다운라이트</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>IoT_다운라이트 3인치 (5W)</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>3인치 | 5W</t>
         </is>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F10" s="16" t="n">
         <v>18000</v>
       </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>상세보기 →</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>상세보기 →</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>원형 다운라이트</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>IoT_다운라이트 6인치 (12W)</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>6인치 | 12W</t>
         </is>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F11" s="9" t="n">
         <v>32500</v>
       </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>상세보기 →</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr"/>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>상세보기 →</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="12" t="inlineStr"/>
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>스팟 다운라이트</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>IoT 핀포인트 매립형 스팟조명</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>2wire CCT | 8W 640lm</t>
         </is>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F12" s="16" t="n">
         <v>38000</v>
       </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>상세보기 →</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="18" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="19" t="inlineStr"/>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>상세보기 →</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="19" t="inlineStr"/>
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>스팟 다운라이트</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>IoT 매립 다운라이트 스팟 조명 [품절]</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>12W | 사틴 니켈</t>
         </is>
       </c>
-      <c r="F12" s="23" t="n">
+      <c r="F13" s="23" t="n">
         <v>75000</v>
       </c>
-      <c r="G12" s="24" t="inlineStr">
-        <is>
-          <t>상세보기 →</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr"/>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>상세보기 →</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="12" t="inlineStr"/>
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>스팟 다운라이트</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>IoT_MR16 COB 2인치 (5W)</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>2인치 | 5W COB</t>
         </is>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F14" s="16" t="n">
         <v>24500</v>
       </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>상세보기 →</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>상세보기 →</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>스팟 다운라이트</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>IoT_MR16 COB 3인치 (5W)</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>3인치 | 5W COB</t>
         </is>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F15" s="9" t="n">
         <v>26200</v>
       </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>상세보기 →</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr"/>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>상세보기 →</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="12" t="inlineStr"/>
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>사각 다운라이트</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>IoT_스페이스4구(16W)</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>4구 | 16W | 사각 매립형</t>
         </is>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F16" s="16" t="n">
         <v>64600</v>
       </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>상세보기 →</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>상세보기 →</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>사각 다운라이트</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>IoT_스페이스 5구(20W)</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>5구 | 20W | 사각 매립형</t>
         </is>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F17" s="9" t="n">
         <v>80700</v>
       </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>상세보기 →</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="12" t="inlineStr"/>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>상세보기 →</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="12" t="inlineStr"/>
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>라인/마그네틱</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>IoT 그리드슬롯6구</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>12W | 960lm | 2-Wire 디밍</t>
         </is>
       </c>
-      <c r="F17" s="16" t="n">
-        <v>35000</v>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>상세보기 →</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="F18" s="16" t="n">
+        <v>30100</v>
+      </c>
+      <c r="G18" s="17" t="inlineStr">
+        <is>
+          <t>상세보기 →</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>라인/마그네틱</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>IoT 그리드슬롯12구</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>고출력 매입형 LED 라인 다운라이트</t>
         </is>
       </c>
-      <c r="F18" s="9" t="n">
-        <v>45000</v>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>상세보기 →</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="19" t="inlineStr"/>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>라인/마그네틱</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>IoT 플렉시블 라인 투명 실리콘 조명 10폭 5m [품절]</t>
-        </is>
-      </c>
-      <c r="E19" s="22" t="inlineStr">
-        <is>
-          <t>5m | 투명 실리콘</t>
-        </is>
-      </c>
-      <c r="F19" s="23" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G19" s="24" t="inlineStr">
+      <c r="F19" s="9" t="n">
+        <v>46300</v>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>상세보기 →</t>
         </is>
@@ -1721,164 +1749,165 @@
       </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
+          <t>IoT 플렉시블 라인 투명 실리콘 조명 10폭 5m [품절]</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>5m | 투명 실리콘</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>상세보기 →</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="19" t="inlineStr"/>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>라인/마그네틱</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
           <t>IoT 스타일컷 라인 실리콘 조명 10폭 5m [품절]</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>5m | 불투명 실리콘 | 1cm·2cm 폭</t>
         </is>
       </c>
-      <c r="F20" s="23" t="n">
+      <c r="F21" s="23" t="n">
         <v>77500</v>
       </c>
-      <c r="G20" s="24" t="inlineStr">
-        <is>
-          <t>상세보기 →</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="12" t="inlineStr"/>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>상세보기 →</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="12" t="inlineStr"/>
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>스마트홈 기기</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>IoT 스마트 전동커튼</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>1.8~4.5m | Touch &amp; Go | 30dB이하 DC모터 | 30kg</t>
         </is>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F22" s="16" t="n">
         <v>164000</v>
       </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>상세보기 →</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>상세보기 →</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>스마트홈 기기</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>IoT 스마트 실링팬 Smart Air (46인치/52인치)</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>46/52인치 | 앱·리모컨 동시 제어</t>
         </is>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F23" s="9" t="n">
         <v>220000</v>
       </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>상세보기 →</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="12" t="inlineStr"/>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>상세보기 →</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="12" t="inlineStr"/>
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>컨버터/액세서리</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>컨버터 36W IoT</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>36W</t>
         </is>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F24" s="16" t="n">
         <v>24500</v>
       </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>상세보기 →</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="5" t="inlineStr"/>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>상세보기 →</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>컨버터/액세서리</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>컨버터 60W IoT</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>60W</t>
         </is>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F25" s="9" t="n">
         <v>30100</v>
       </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>상세보기 →</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>22</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>컨버터/액세서리</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>컨버터 150W IoT</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>150W</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>44100</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>상세보기 →</t>
         </is>
       </c>
     </row>
@@ -1893,18 +1922,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>컨버터 150W IoT</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>150W</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>44100</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>24</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>컨버터/액세서리</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>컨트롤러 2-Wire</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>2-Wire 디밍</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F27" t="n">
         <v>35000</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
